--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\Potencjał biogazu\2. 2026\BASIC_AGR\Basic_AGR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\2026\2. AGR_model_wyizolowany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B5FC6BD-A887-4A9F-BCC4-EBB578541BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18855487-30F3-4A7F-9813-6E4D875839A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="18420" windowHeight="10008" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="101">
   <si>
     <t>IMP*Z</t>
   </si>
@@ -293,9 +293,6 @@
     <t>Commodity_Unit</t>
   </si>
   <si>
-    <t>REG1</t>
-  </si>
-  <si>
     <t>YRFR</t>
   </si>
   <si>
@@ -308,9 +305,6 @@
     <t>PRI</t>
   </si>
   <si>
-    <t>REG2</t>
-  </si>
-  <si>
     <t>DumVarforUC</t>
   </si>
   <si>
@@ -438,6 +432,9 @@
   </si>
   <si>
     <t>000_Units</t>
+  </si>
+  <si>
+    <t>PL</t>
   </si>
 </sst>
 </file>
@@ -2510,12 +2507,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:J5"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.109375" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="8" max="8" width="29.44140625" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:10">
@@ -2547,13 +2544,13 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2568,12 +2565,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:B14"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2">
@@ -2627,10 +2624,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:C9"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.44140625" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:3">
@@ -2680,7 +2677,7 @@
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C9" s="15">
         <v>0</v>
@@ -2697,15 +2694,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B13:Q19"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <dimension ref="B13:P19"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.6640625" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="13" spans="2:4" ht="15">
@@ -2713,7 +2710,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="17.399999999999999">
+    <row r="15" spans="2:4" ht="18">
       <c r="B15" s="8" t="s">
         <v>43</v>
       </c>
@@ -2722,10 +2719,10 @@
     </row>
     <row r="16" spans="2:4" ht="19.5" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" customHeight="1" thickBot="1">
       <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
@@ -2736,7 +2733,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>2</v>
@@ -2745,61 +2742,58 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q17" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:17">
+    <row r="18" spans="2:16">
       <c r="D18" t="s">
         <v>3</v>
       </c>
       <c r="G18">
         <v>2222</v>
       </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
       <c r="J18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:16">
       <c r="D19" t="s">
         <v>3</v>
       </c>
       <c r="G19">
         <v>8888</v>
       </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
       <c r="J19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2815,15 +2809,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:G34"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="11"/>
-    <col min="2" max="2" width="12.109375" style="11" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="11"/>
+    <col min="2" max="2" width="12.140625" style="11" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="11" customWidth="1"/>
     <col min="4" max="4" width="14" style="11" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="11"/>
+    <col min="5" max="5" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="15">
@@ -2836,7 +2830,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="13.8" thickBot="1">
+    <row r="6" spans="2:7" ht="13.5" thickBot="1">
       <c r="B6" s="5" t="s">
         <v>19</v>
       </c>
@@ -2850,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>27</v>
@@ -2858,7 +2852,7 @@
     </row>
     <row r="7" spans="2:7">
       <c r="D7" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="11">
         <v>1990</v>
@@ -2874,10 +2868,10 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E9" s="17">
         <v>1</v>
@@ -3014,10 +3008,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:I30"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -3028,7 +3022,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="13.8" thickBot="1">
+    <row r="3" spans="2:9" ht="13.5" thickBot="1">
       <c r="B3" s="12" t="s">
         <v>48</v>
       </c>
@@ -3036,42 +3030,42 @@
         <v>31</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F3" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="H3" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="I3" s="28" t="s">
         <v>95</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>50</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H4" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -3079,65 +3073,65 @@
         <v>51</v>
       </c>
       <c r="E5" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" ht="13.8" thickBot="1">
+    </row>
+    <row r="6" spans="2:9" ht="13.5" thickBot="1">
       <c r="D6" s="31" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="15.6">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="15.75">
       <c r="B9" s="27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
     </row>
-    <row r="10" spans="2:9" ht="13.8" thickBot="1">
+    <row r="10" spans="2:9" ht="13.5" thickBot="1">
       <c r="B10" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>68</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="26">
         <v>1055.55</v>
@@ -3145,10 +3139,10 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="29">
         <v>3.6</v>
@@ -3156,10 +3150,10 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" s="26">
         <v>1000</v>
@@ -3167,10 +3161,10 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" s="29">
         <v>1000</v>
@@ -3178,10 +3172,10 @@
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="26">
         <v>1.05555</v>
@@ -3189,10 +3183,10 @@
     </row>
     <row r="16" spans="2:9">
       <c r="B16" s="29" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="29">
         <v>4.1868000000000002E-2</v>
@@ -3200,10 +3194,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" s="26">
         <v>41.868000000000002</v>
@@ -3211,10 +3205,10 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="29" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="29">
         <v>3.5999999999999999E-3</v>
@@ -3222,10 +3216,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D19" s="26">
         <v>1000000</v>
@@ -3233,10 +3227,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="29" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D20" s="29">
         <v>1000</v>
@@ -3244,10 +3238,10 @@
     </row>
     <row r="21" spans="2:4">
       <c r="B21" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" s="26">
         <v>0.15384600000000001</v>
@@ -3255,10 +3249,10 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D22" s="29">
         <v>-1E-3</v>
@@ -3266,10 +3260,10 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="26">
         <v>1000</v>
@@ -3277,10 +3271,10 @@
     </row>
     <row r="24" spans="2:4">
       <c r="B24" s="29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="29">
         <v>37.681199999999997</v>
@@ -3288,10 +3282,10 @@
     </row>
     <row r="25" spans="2:4">
       <c r="B25" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="26">
         <v>2299</v>
@@ -3299,10 +3293,10 @@
     </row>
     <row r="26" spans="2:4">
       <c r="B26" s="29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D26" s="29">
         <v>2.7777769999999999</v>
@@ -3310,10 +3304,10 @@
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D27" s="26">
         <v>0.27777777799999998</v>
@@ -3321,21 +3315,21 @@
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="29">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:4" ht="13.8" thickBot="1">
+    <row r="29" spans="2:4" ht="13.5" thickBot="1">
       <c r="B29" s="30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D29" s="30">
         <v>4.5</v>
@@ -3343,10 +3337,10 @@
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30">
         <v>3.6</v>
@@ -3362,15 +3356,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:I7"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="11.33203125" customWidth="1"/>
-    <col min="9" max="11" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="15">
@@ -3418,13 +3412,11 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="27" thickBot="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="2:9" ht="26.25" thickBot="1">
       <c r="B7" s="9" t="s">
         <v>41</v>
       </c>
@@ -3450,16 +3442,16 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D9D672-94D7-4F30-B856-C3C2B3FF93F0}">
   <dimension ref="B4:D7"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="4" spans="2:4" ht="15.6">
+    <row r="4" spans="2:4" ht="15.75">
       <c r="B4" s="23" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
     </row>
-    <row r="5" spans="2:4" ht="27" thickBot="1">
+    <row r="5" spans="2:4" ht="26.25" thickBot="1">
       <c r="B5" s="22" t="s">
         <v>21</v>
       </c>
@@ -3472,16 +3464,16 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" s="25">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="13.8" thickBot="1">
+    <row r="7" spans="2:4" ht="13.5" thickBot="1">
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -3492,26 +3484,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -3754,10 +3726,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5FC709-3A05-48A4-B886-52B0F96A16DA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287291C6-29F4-47D2-8433-A74DF70B3305}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3769,10 +3772,16 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="2993e53c-5804-4a67-93fb-28b8362cd015"/>
     <ds:schemaRef ds:uri="170e58e9-e7cd-474a-92db-e9a604da91e6"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287291C6-29F4-47D2-8433-A74DF70B3305}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5FC709-3A05-48A4-B886-52B0F96A16DA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\2026\2. AGR_model_wyizolowany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18855487-30F3-4A7F-9813-6E4D875839A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FB32CC-9F5F-4250-AD63-14B6A2D40900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -308,9 +308,6 @@
     <t>DumVarforUC</t>
   </si>
   <si>
-    <t>REG</t>
-  </si>
-  <si>
     <t>ANNUAL</t>
   </si>
   <si>
@@ -435,6 +432,9 @@
   </si>
   <si>
     <t>PL</t>
+  </si>
+  <si>
+    <t>Model</t>
   </si>
 </sst>
 </file>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H5" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="16" spans="2:4" ht="19.5" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:16" ht="15.75" customHeight="1" thickBot="1">
@@ -2733,7 +2733,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>2</v>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>22</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>27</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>53</v>
@@ -3033,21 +3033,21 @@
         <v>56</v>
       </c>
       <c r="F3" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="H3" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="I3" s="28" t="s">
         <v>94</v>
-      </c>
-      <c r="I3" s="28" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>50</v>
@@ -3065,7 +3065,7 @@
         <v>55</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -3073,19 +3073,19 @@
         <v>51</v>
       </c>
       <c r="E5" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="G5" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="29" t="s">
         <v>98</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.5" thickBot="1">
@@ -3105,30 +3105,30 @@
         <v>55</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="15.75">
       <c r="B9" s="27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
     </row>
     <row r="10" spans="2:9" ht="13.5" thickBot="1">
       <c r="B10" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="D10" s="28" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>55</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>55</v>
@@ -3150,10 +3150,10 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>71</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>72</v>
       </c>
       <c r="D13" s="26">
         <v>1000</v>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="29" t="s">
         <v>73</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>74</v>
       </c>
       <c r="D14" s="29">
         <v>1000</v>
@@ -3172,7 +3172,7 @@
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>55</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="16" spans="2:9">
       <c r="B16" s="29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>55</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="26" t="s">
         <v>55</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="29" t="s">
         <v>55</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D19" s="26">
         <v>1000000</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="29" t="s">
         <v>80</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>81</v>
       </c>
       <c r="D20" s="29">
         <v>1000</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="21" spans="2:4">
       <c r="B21" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>82</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>83</v>
       </c>
       <c r="D21" s="26">
         <v>0.15384600000000001</v>
@@ -3249,10 +3249,10 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" s="29" t="s">
         <v>84</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>85</v>
       </c>
       <c r="D22" s="29">
         <v>-1E-3</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="26" t="s">
         <v>55</v>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="24" spans="2:4">
       <c r="B24" s="29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="29" t="s">
         <v>55</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="25" spans="2:4">
       <c r="B25" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="26" t="s">
         <v>55</v>
@@ -3293,10 +3293,10 @@
     </row>
     <row r="26" spans="2:4">
       <c r="B26" s="29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D26" s="29">
         <v>2.7777769999999999</v>
@@ -3307,7 +3307,7 @@
         <v>55</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="26">
         <v>0.27777777799999998</v>
@@ -3326,10 +3326,10 @@
     </row>
     <row r="29" spans="2:4" ht="13.5" thickBot="1">
       <c r="B29" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="30">
         <v>4.5</v>
@@ -3337,10 +3337,10 @@
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30">
         <v>3.6</v>
@@ -3412,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>62</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>63</v>
       </c>
       <c r="D6" s="25">
         <v>1</v>
@@ -3484,6 +3484,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -3726,17 +3737,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3747,6 +3747,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23DBFA9A-F91F-4FD3-948F-E61D64FE0893}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2993e53c-5804-4a67-93fb-28b8362cd015"/>
+    <ds:schemaRef ds:uri="170e58e9-e7cd-474a-92db-e9a604da91e6"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287291C6-29F4-47D2-8433-A74DF70B3305}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3765,19 +3778,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23DBFA9A-F91F-4FD3-948F-E61D64FE0893}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2993e53c-5804-4a67-93fb-28b8362cd015"/>
-    <ds:schemaRef ds:uri="170e58e9-e7cd-474a-92db-e9a604da91e6"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5FC709-3A05-48A4-B886-52B0F96A16DA}">
   <ds:schemaRefs>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patir\Documents\Praca ESMlab\1. TIMES-PL-PSE\2026\2. AGR_model_wyizolowany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FB32CC-9F5F-4250-AD63-14B6A2D40900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A339B0C-6586-4AB3-8AE7-5681B8BEB664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="853" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -602,7 +602,7 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -734,6 +734,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF95B3D7"/>
         <bgColor rgb="FF9999FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -869,7 +893,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -910,6 +934,10 @@
     <xf numFmtId="0" fontId="12" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="27">
     <cellStyle name="20% - Accent5 2" xfId="5" xr:uid="{E0C8E57F-AF10-4B69-8852-5AB750A8B5CF}"/>
@@ -2564,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:B14"/>
+  <dimension ref="B3:E39"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="2" max="2" width="16.85546875" customWidth="1"/>
@@ -2573,44 +2601,193 @@
     <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:2">
+    <row r="3" spans="2:5">
       <c r="B3" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="2:5">
       <c r="B4">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
       <c r="B7" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="8" spans="2:5">
       <c r="B8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="2:5">
       <c r="B11" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="2:5">
       <c r="B12" s="21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="2:5">
       <c r="B13" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:2">
+      <c r="E13" s="32">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
       <c r="B14" s="15">
+        <v>1</v>
+      </c>
+      <c r="E14" s="33">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" s="15">
         <v>2</v>
+      </c>
+      <c r="E15" s="32">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" s="15">
+        <v>5</v>
+      </c>
+      <c r="E16" s="32">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="15">
+        <v>5</v>
+      </c>
+      <c r="E17" s="34">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="15">
+        <v>5</v>
+      </c>
+      <c r="E18" s="34">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="15">
+        <v>5</v>
+      </c>
+      <c r="E19" s="34">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="15">
+        <v>5</v>
+      </c>
+      <c r="E20" s="34">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="E21" s="34">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="E22" s="35">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="E23" s="35">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="E24" s="35">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="E25" s="35">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="E26" s="35">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="E27" s="34">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="E28" s="34">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="E29" s="34">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="E30" s="34">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="E31" s="34">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="E32" s="32">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" s="32">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5">
+      <c r="E34" s="32">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5">
+      <c r="E35" s="32">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5">
+      <c r="E36" s="32">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5">
+      <c r="E37">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5">
+      <c r="E38">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5">
+      <c r="E39">
+        <v>2050</v>
       </c>
     </row>
   </sheetData>
@@ -3484,17 +3661,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="16" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="d5167bf0dd55feede3e29f1a430471b5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="24bde18039da748f015df48b5e1e3648" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -3737,6 +3903,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8acd6055-54fc-4ce7-b3df-0a09834a0329">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3747,19 +3924,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23DBFA9A-F91F-4FD3-948F-E61D64FE0893}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2993e53c-5804-4a67-93fb-28b8362cd015"/>
-    <ds:schemaRef ds:uri="170e58e9-e7cd-474a-92db-e9a604da91e6"/>
-    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
-    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{287291C6-29F4-47D2-8433-A74DF70B3305}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3778,6 +3942,19 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23DBFA9A-F91F-4FD3-948F-E61D64FE0893}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2993e53c-5804-4a67-93fb-28b8362cd015"/>
+    <ds:schemaRef ds:uri="170e58e9-e7cd-474a-92db-e9a604da91e6"/>
+    <ds:schemaRef ds:uri="708d6b01-37ca-4db4-bc7f-9b68f32c58b8"/>
+    <ds:schemaRef ds:uri="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D5FC709-3A05-48A4-B886-52B0F96A16DA}">
   <ds:schemaRefs>
